--- a/isms-core-framework/A.5-organisational-controls/isms-a.5.7-threat-intelligence/WKBK/ISMS-IMP-A.5.7.1_Threat_Intelligence_Sources_Assessment_20260301.xlsx
+++ b/isms-core-framework/A.5-organisational-controls/isms-a.5.7-threat-intelligence/WKBK/ISMS-IMP-A.5.7.1_Threat_Intelligence_Sources_Assessment_20260301.xlsx
@@ -19806,7 +19806,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>01.03.2026 12:11:31</t>
+          <t>01.03.2026 17:57:37</t>
         </is>
       </c>
     </row>
